--- a/artfynd/A 48789-2021 artfynd.xlsx
+++ b/artfynd/A 48789-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48789-2021 artfynd.xlsx
+++ b/artfynd/A 48789-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>75335456</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>874724.6757832462</v>
+        <v>874725</v>
       </c>
       <c r="R2" t="n">
-        <v>7376948.139989234</v>
+        <v>7376948</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,19 +746,9 @@
           <t>2018-10-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-10-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,43 +780,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>75330141</v>
+        <v>75335830</v>
       </c>
       <c r="B3" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>103031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -839,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>874724.6757832462</v>
+        <v>874725</v>
       </c>
       <c r="R3" t="n">
-        <v>7376948.139989234</v>
+        <v>7376948</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,19 +868,9 @@
           <t>2018-10-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-10-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,7 +879,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -909,6 +894,112 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>NVI Kiilisjärvi-Ekfors, 2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>75330141</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>V Puostijärvi alapää, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>874725</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7376948</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hietaniemi</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2018-10-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2018-10-04</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Louise Berglund</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Louise Berglund</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>NVI Kiilisjärvi-Ekfors, 2018</t>
         </is>

--- a/artfynd/A 48789-2021 artfynd.xlsx
+++ b/artfynd/A 48789-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
           <t>NVI Kiilisjärvi-Ekfors, 2018</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75335456</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>NVI Kiilisjärvi-Ekfors, 2018</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75335830</t>
         </is>
       </c>
     </row>
@@ -1004,8 +1019,18 @@
           <t>NVI Kiilisjärvi-Ekfors, 2018</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75330141</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>